--- a/data/trans_bre/P36B08_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 10,55</t>
+          <t>-2,41; 11,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 15,63</t>
+          <t>4,12; 15,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 8,79</t>
+          <t>-2,91; 8,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,43</t>
+          <t>-0,72; 3,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 15,73</t>
+          <t>-3,21; 17,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 21,3</t>
+          <t>5,09; 21,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 11,76</t>
+          <t>-3,45; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,68</t>
+          <t>-0,73; 3,75</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 11,49</t>
+          <t>-2,62; 12,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 9,95</t>
+          <t>-2,78; 9,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 6,66</t>
+          <t>-6,2; 6,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,3</t>
+          <t>-0,9; 4,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 18,87</t>
+          <t>-3,87; 19,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 13,9</t>
+          <t>-3,53; 14,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 8,7</t>
+          <t>-7,55; 8,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,6</t>
+          <t>-0,93; 4,37</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,79%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 15,45</t>
+          <t>-1,97; 15,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 13,03</t>
+          <t>-0,05; 12,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 16,7</t>
+          <t>1,83; 16,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 1,62</t>
+          <t>-3,62; 3,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 26,02</t>
+          <t>-3,01; 25,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 18,14</t>
+          <t>0,17; 17,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 25,0</t>
+          <t>2,65; 25,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 1,7</t>
+          <t>-3,77; 3,34</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,44</t>
+          <t>2,01; 10,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 12,24</t>
+          <t>3,47; 12,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,76</t>
+          <t>1,06; 9,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,99</t>
+          <t>-0,93; 3,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 16,84</t>
+          <t>2,97; 17,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 17,52</t>
+          <t>4,8; 17,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,56</t>
+          <t>1,5; 12,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,4</t>
+          <t>-0,97; 3,51</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 18,96</t>
+          <t>5,64; 19,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 13,34</t>
+          <t>2,99; 13,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 10,8</t>
+          <t>0,51; 10,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,52</t>
+          <t>-0,58; 5,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 35,6</t>
+          <t>8,7; 35,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 20,18</t>
+          <t>4,04; 19,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 15,5</t>
+          <t>0,68; 14,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 7,29</t>
+          <t>-0,6; 5,92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,21; 25,39</t>
+          <t>13,31; 25,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,59; 35,02</t>
+          <t>22,06; 34,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,81; 20,0</t>
+          <t>6,45; 19,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 14,96</t>
+          <t>0,69; 14,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,11; 54,18</t>
+          <t>23,51; 54,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,7; 78,27</t>
+          <t>39,55; 78,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,9; 34,93</t>
+          <t>9,53; 34,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 18,74</t>
+          <t>0,65; 18,07</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,92</t>
+          <t>5,58; 10,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,49</t>
+          <t>6,34; 10,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,2</t>
+          <t>3,0; 7,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,93</t>
+          <t>0,39; 2,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 15,91</t>
+          <t>8,54; 16,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,69; 15,0</t>
+          <t>8,72; 14,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,12</t>
+          <t>4,04; 10,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,15</t>
+          <t>0,41; 2,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P36B08_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
